--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,6 +322,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:type</t>
   </si>
   <si>
@@ -368,9 +371,6 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:type.value[x]</t>
   </si>
   <si>
@@ -462,8 +462,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>./low</t>
@@ -1308,24 +1308,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1350,10 +1350,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1413,7 +1413,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1559,7 +1559,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1619,7 +1619,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1656,16 +1656,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1715,7 +1715,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1730,7 +1730,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1825,13 +1825,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1870,7 +1870,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1930,7 +1930,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -1944,7 +1944,7 @@
         <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2047,7 +2047,7 @@
         <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2076,7 +2076,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2136,7 +2136,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2150,7 +2150,7 @@
         <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2173,16 +2173,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2232,7 +2232,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2247,7 +2247,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2344,13 +2344,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -2552,13 +2552,13 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2809,7 +2809,7 @@
         <v>157</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2869,7 +2869,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>82</v>
@@ -2883,7 +2883,7 @@
         <v>158</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2986,7 +2986,7 @@
         <v>159</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3015,7 +3015,7 @@
         <v>30</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3075,7 +3075,7 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>82</v>
@@ -3089,7 +3089,7 @@
         <v>160</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3112,16 +3112,16 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3171,7 +3171,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -3186,7 +3186,7 @@
         <v>76</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -3281,13 +3281,13 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -3326,7 +3326,7 @@
         <v>165</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3386,7 +3386,7 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -3400,7 +3400,7 @@
         <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3503,7 +3503,7 @@
         <v>167</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3532,7 +3532,7 @@
         <v>30</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3592,7 +3592,7 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
@@ -3606,7 +3606,7 @@
         <v>168</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3629,16 +3629,16 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3688,7 +3688,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -3703,7 +3703,7 @@
         <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -3798,21 +3798,21 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3835,16 +3835,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3894,7 +3894,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -3909,7 +3909,7 @@
         <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -4006,13 +4006,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
